--- a/exports/KPI_Result_2025_7.xlsx
+++ b/exports/KPI_Result_2025_7.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -481,127 +481,227 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mai Khanh (MK)</v>
+        <v>Ha Ny (SH)</v>
       </c>
       <c r="B5" t="str">
-        <v>MK</v>
+        <v>SH</v>
       </c>
       <c r="C5" t="str">
-        <v>R&amp;D</v>
+        <v>Sales</v>
       </c>
       <c r="D5">
-        <v>559.9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1267.95</v>
+        <v>820.46</v>
       </c>
       <c r="F5" t="str">
-        <v>44.16%</v>
+        <v>0.00%</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nhiễm (AN)</v>
+        <v>Mai Khanh (MK)</v>
       </c>
       <c r="B6" t="str">
-        <v>AN</v>
+        <v>MK</v>
       </c>
       <c r="C6" t="str">
         <v>R&amp;D</v>
       </c>
       <c r="D6">
-        <v>39.37</v>
+        <v>559.9</v>
       </c>
       <c r="E6">
         <v>1267.95</v>
       </c>
       <c r="F6" t="str">
-        <v>3.11%</v>
+        <v>44.16%</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Nhung (NU)</v>
+        <v>Mai Khanh (MK)</v>
       </c>
       <c r="B7" t="str">
-        <v>NU</v>
+        <v>MK</v>
       </c>
       <c r="C7" t="str">
-        <v>CSM - Bán hàng</v>
+        <v>Sales</v>
       </c>
       <c r="D7">
-        <v>5225.64</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5628.8</v>
+        <v>820.46</v>
       </c>
       <c r="F7" t="str">
-        <v>92.84%</v>
+        <v>0.00%</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Thiên Hà (HV)</v>
+        <v>Nguyễn Hằng (HN)</v>
       </c>
       <c r="B8" t="str">
-        <v>HV</v>
+        <v>HN</v>
       </c>
       <c r="C8" t="str">
-        <v>CSM - Bán hàng</v>
+        <v>Service Staff</v>
       </c>
       <c r="D8">
-        <v>5225.64</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>5628.8</v>
+        <v>16000</v>
       </c>
       <c r="F8" t="str">
-        <v>92.84%</v>
+        <v>0.00%</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Thành  (BX)</v>
+        <v>Nhiễm (AN)</v>
       </c>
       <c r="B9" t="str">
-        <v>BX</v>
+        <v>AN</v>
       </c>
       <c r="C9" t="str">
         <v>R&amp;D</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>39.37</v>
       </c>
       <c r="E9">
-        <v>1899.48</v>
+        <v>1267.95</v>
       </c>
       <c r="F9" t="str">
-        <v>0.00%</v>
+        <v>3.11%</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Nhiễm (AN)</v>
+      </c>
+      <c r="B10" t="str">
+        <v>AN</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>820.46</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0.00%</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Nhung (NU)</v>
+      </c>
+      <c r="B11" t="str">
+        <v>NU</v>
+      </c>
+      <c r="C11" t="str">
+        <v>CSM - Bán hàng</v>
+      </c>
+      <c r="D11">
+        <v>5225.64</v>
+      </c>
+      <c r="E11">
+        <v>5628.8</v>
+      </c>
+      <c r="F11" t="str">
+        <v>92.84%</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Thao Hong (TA)</v>
+      </c>
+      <c r="B12" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Service Staff</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>16000</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0.00%</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Thiên Hà (HV)</v>
+      </c>
+      <c r="B13" t="str">
+        <v>HV</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CSM - Bán hàng</v>
+      </c>
+      <c r="D13">
+        <v>5225.64</v>
+      </c>
+      <c r="E13">
+        <v>5628.8</v>
+      </c>
+      <c r="F13" t="str">
+        <v>92.84%</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Thành  (BX)</v>
+      </c>
+      <c r="B14" t="str">
+        <v>BX</v>
+      </c>
+      <c r="C14" t="str">
+        <v>R&amp;D</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1899.48</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0.00%</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
         <v>Truong (XT)</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B15" t="str">
         <v>XT</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C15" t="str">
         <v>Designer</v>
       </c>
-      <c r="D10">
+      <c r="D15">
         <v>2748.07</v>
       </c>
-      <c r="E10">
+      <c r="E15">
         <v>3769.29</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F15" t="str">
         <v>72.91%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/exports/KPI_Result_2025_7.xlsx
+++ b/exports/KPI_Result_2025_7.xlsx
@@ -1,41 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QUOC\Desktop\Tekup\KPI_new\exports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8700EA-FC9C-4884-8514-8B0739AAE2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="KPI" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>PIC_Key</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>Cong Nam Nguyen (CN)</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Tổng lợi nhuận gộp tháng 7 từ các sản phẩm do người thực hiện KPI lên ý tưởng</t>
+  </si>
+  <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>34.49%</t>
+  </si>
+  <si>
+    <t>Doan Ha (HD)</t>
+  </si>
+  <si>
+    <t>HD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng lợi nhuận gộp tháng 7 từ các mẫu gốc và từ các mẫu của đơn custom do designer thiết kế </t>
+  </si>
+  <si>
+    <t>Designer</t>
+  </si>
+  <si>
+    <t>34.07%</t>
+  </si>
+  <si>
+    <t>Ha Ny (SH)</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>-0.28%</t>
+  </si>
+  <si>
+    <t>Tổng lợi nhuận gộp từ khách hàng do người thực hiện KPI chốt được trong 3 tháng 5, 6, 7</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Mai Khanh (MK)</t>
+  </si>
+  <si>
+    <t>MK</t>
+  </si>
+  <si>
+    <t>44.16%</t>
+  </si>
+  <si>
+    <t>Nguyễn Hằng (HN)</t>
+  </si>
+  <si>
+    <t>HN</t>
+  </si>
+  <si>
+    <t>Tổng lợi nhuận gộp của toàn bộ mảng dịch vụ trong tháng 7</t>
+  </si>
+  <si>
+    <t>Service Staff</t>
+  </si>
+  <si>
+    <t>Nhiễm (AN)</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>3.11%</t>
+  </si>
+  <si>
+    <t>Nhung (NU)</t>
+  </si>
+  <si>
+    <t>NU</t>
+  </si>
+  <si>
+    <t>Tổng lợi nhuận gộp của toàn bộ mảng bán hàng trong tháng 7 (không bao gồm Merch)</t>
+  </si>
+  <si>
+    <t>CSM - Bán hàng</t>
+  </si>
+  <si>
+    <t>92.84%</t>
+  </si>
+  <si>
+    <t>Thao Hong (TA)</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>Thiên Hà (HV)</t>
+  </si>
+  <si>
+    <t>HV</t>
+  </si>
+  <si>
+    <t>Thành  (BX)</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>Truong (XT)</t>
+  </si>
+  <si>
+    <t>XT</t>
+  </si>
+  <si>
+    <t>72.91%</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +216,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,312 +555,526 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.09765625" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" customWidth="1"/>
+    <col min="3" max="3" width="86.8984375" customWidth="1"/>
+    <col min="4" max="4" width="15.8984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PIC</v>
-      </c>
-      <c r="B1" t="str">
-        <v>PIC_Key</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Position</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Profit</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Target</v>
-      </c>
-      <c r="F1" t="str">
-        <v>KPI</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Cong Nam Nguyen (CN)</v>
-      </c>
-      <c r="B2" t="str">
-        <v>CN</v>
-      </c>
-      <c r="C2" t="str">
-        <v>R&amp;D</v>
-      </c>
-      <c r="D2">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2">
         <v>488.74</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1417.14</v>
       </c>
-      <c r="F2" t="str">
-        <v>34.49%</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Doan Ha (HD)</v>
-      </c>
-      <c r="B3" t="str">
-        <v>HD</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Designer</v>
-      </c>
-      <c r="D3">
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3">
         <v>1113.05</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>3266.71</v>
       </c>
-      <c r="F3" t="str">
-        <v>34.07%</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Ha Ny (SH)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>SH</v>
-      </c>
-      <c r="C4" t="str">
-        <v>R&amp;D</v>
-      </c>
-      <c r="D4">
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
         <v>-3.59</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1267.95</v>
       </c>
-      <c r="F4" t="str">
-        <v>-0.28%</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Ha Ny (SH)</v>
-      </c>
-      <c r="B5" t="str">
-        <v>SH</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Sales</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>820.46</v>
       </c>
-      <c r="F5" t="str">
-        <v>0.00%</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Mai Khanh (MK)</v>
-      </c>
-      <c r="B6" t="str">
-        <v>MK</v>
-      </c>
-      <c r="C6" t="str">
-        <v>R&amp;D</v>
-      </c>
-      <c r="D6">
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
         <v>559.9</v>
       </c>
-      <c r="E6">
+      <c r="F7">
         <v>1267.95</v>
       </c>
-      <c r="F6" t="str">
-        <v>44.16%</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Mai Khanh (MK)</v>
-      </c>
-      <c r="B7" t="str">
-        <v>MK</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Sales</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>820.46</v>
       </c>
-      <c r="F7" t="str">
-        <v>0.00%</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Nguyễn Hằng (HN)</v>
-      </c>
-      <c r="B8" t="str">
-        <v>HN</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Service Staff</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>16000</v>
       </c>
-      <c r="F8" t="str">
-        <v>0.00%</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Nhiễm (AN)</v>
-      </c>
-      <c r="B9" t="str">
-        <v>AN</v>
-      </c>
-      <c r="C9" t="str">
-        <v>R&amp;D</v>
-      </c>
-      <c r="D9">
-        <v>39.37</v>
-      </c>
-      <c r="E9">
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>820.46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>39.369999999999997</v>
+      </c>
+      <c r="F13">
         <v>1267.95</v>
       </c>
-      <c r="F9" t="str">
-        <v>3.11%</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Nhiễm (AN)</v>
-      </c>
-      <c r="B10" t="str">
-        <v>AN</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Sales</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>820.46</v>
       </c>
-      <c r="F10" t="str">
-        <v>0.00%</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Nhung (NU)</v>
-      </c>
-      <c r="B11" t="str">
-        <v>NU</v>
-      </c>
-      <c r="C11" t="str">
-        <v>CSM - Bán hàng</v>
-      </c>
-      <c r="D11">
-        <v>5225.64</v>
-      </c>
-      <c r="E11">
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16">
+        <v>5225.6400000000003</v>
+      </c>
+      <c r="F16">
         <v>5628.8</v>
       </c>
-      <c r="F11" t="str">
-        <v>92.84%</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Thao Hong (TA)</v>
-      </c>
-      <c r="B12" t="str">
-        <v>TA</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Service Staff</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
+      <c r="G16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>16000</v>
       </c>
-      <c r="F12" t="str">
-        <v>0.00%</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Thiên Hà (HV)</v>
-      </c>
-      <c r="B13" t="str">
-        <v>HV</v>
-      </c>
-      <c r="C13" t="str">
-        <v>CSM - Bán hàng</v>
-      </c>
-      <c r="D13">
-        <v>5225.64</v>
-      </c>
-      <c r="E13">
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>968.15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20">
+        <v>5225.6400000000003</v>
+      </c>
+      <c r="F20">
         <v>5628.8</v>
       </c>
-      <c r="F13" t="str">
-        <v>92.84%</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Thành  (BX)</v>
-      </c>
-      <c r="B14" t="str">
-        <v>BX</v>
-      </c>
-      <c r="C14" t="str">
-        <v>R&amp;D</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
+      <c r="G20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>1899.48</v>
       </c>
-      <c r="F14" t="str">
-        <v>0.00%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Truong (XT)</v>
-      </c>
-      <c r="B15" t="str">
-        <v>XT</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Designer</v>
-      </c>
-      <c r="D15">
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22">
         <v>2748.07</v>
       </c>
-      <c r="E15">
+      <c r="F22">
         <v>3769.29</v>
       </c>
-      <c r="F15" t="str">
-        <v>72.91%</v>
+      <c r="G22" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
+    <ignoredError sqref="A1:G22" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/exports/KPI_Result_2025_7.xlsx
+++ b/exports/KPI_Result_2025_7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QUOC\Desktop\Tekup\KPI_new\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8700EA-FC9C-4884-8514-8B0739AAE2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE9D94C-5BF7-4BFB-A913-026DE83B769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="52">
   <si>
     <t>PIC</t>
   </si>
@@ -131,6 +131,12 @@
     <t>Service Staff</t>
   </si>
   <si>
+    <t>96.56%</t>
+  </si>
+  <si>
+    <t>36.92%</t>
+  </si>
+  <si>
     <t>Nhiễm (AN)</t>
   </si>
   <si>
@@ -159,6 +165,9 @@
   </si>
   <si>
     <t>TA</t>
+  </si>
+  <si>
+    <t>328.51%</t>
   </si>
   <si>
     <t>Thiên Hà (HV)</t>
@@ -559,10 +568,10 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.09765625" customWidth="1"/>
-    <col min="2" max="2" width="10.3984375" customWidth="1"/>
-    <col min="3" max="3" width="86.8984375" customWidth="1"/>
-    <col min="4" max="4" width="15.8984375" customWidth="1"/>
+    <col min="1" max="1" width="24.69921875" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="73.5" customWidth="1"/>
+    <col min="4" max="4" width="16.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -786,13 +795,13 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>15449.978999999974</v>
       </c>
       <c r="F10">
         <v>16000</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -809,13 +818,13 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>302.94000000000017</v>
       </c>
       <c r="F11">
         <v>820.46</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -843,10 +852,10 @@
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -861,15 +870,15 @@
         <v>1267.95</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -889,10 +898,10 @@
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -912,16 +921,16 @@
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E16">
         <v>5225.6400000000003</v>
@@ -930,15 +939,15 @@
         <v>5628.8</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
@@ -947,21 +956,21 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>15449.978999999974</v>
       </c>
       <c r="F17">
         <v>16000</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -970,21 +979,21 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>3180.4399999999996</v>
       </c>
       <c r="F18">
         <v>968.15</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -1004,16 +1013,16 @@
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E20">
         <v>5225.6400000000003</v>
@@ -1022,15 +1031,15 @@
         <v>5628.8</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
@@ -1050,10 +1059,10 @@
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -1068,7 +1077,7 @@
         <v>3769.29</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
